--- a/data/trans_orig/P19C03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93417</t>
+          <t>93279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130459</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>73680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101773</t>
+          <t>104395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178806</t>
+          <t>177519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223576</t>
+          <t>224712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255843</t>
+          <t>258174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292885</t>
+          <t>293023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166514</t>
+          <t>163892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196789</t>
+          <t>194607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431014</t>
+          <t>429878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475784</t>
+          <t>477071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83925</t>
+          <t>82905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117135</t>
+          <t>119286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106424</t>
+          <t>106231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141368</t>
+          <t>140009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201019</t>
+          <t>201349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248179</t>
+          <t>248752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183070</t>
+          <t>180919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216280</t>
+          <t>217300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192197</t>
+          <t>193556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227141</t>
+          <t>227334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385591</t>
+          <t>385018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432751</t>
+          <t>432421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>132615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172025</t>
+          <t>173369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>56386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174869</t>
+          <t>175401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221417</t>
+          <t>220530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>258242</t>
+          <t>256898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>297652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84618</t>
+          <t>83682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106564</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348918</t>
+          <t>349805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>395466</t>
+          <t>394934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242252</t>
+          <t>245222</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298048</t>
+          <t>297669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191001</t>
+          <t>189387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241015</t>
+          <t>239076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>450294</t>
+          <t>447324</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>524240</t>
+          <t>520573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>572365</t>
+          <t>572744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628161</t>
+          <t>625191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355234</t>
+          <t>357173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>405248</t>
+          <t>406862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942422</t>
+          <t>946089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1016368</t>
+          <t>1019338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99536</t>
+          <t>96989</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136169</t>
+          <t>136110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177677</t>
+          <t>177003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213757</t>
+          <t>212221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266260</t>
+          <t>262348</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148391</t>
+          <t>150938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179403</t>
+          <t>179938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278403</t>
+          <t>279077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319911</t>
+          <t>319970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>437747</t>
+          <t>441659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>490250</t>
+          <t>491786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52109</t>
+          <t>52821</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78889</t>
+          <t>77719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227010</t>
+          <t>229120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280619</t>
+          <t>282085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>291130</t>
+          <t>288798</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348320</t>
+          <t>349448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133344</t>
+          <t>134514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160124</t>
+          <t>159412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>664997</t>
+          <t>663531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>718606</t>
+          <t>716496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>809529</t>
+          <t>808401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>866719</t>
+          <t>869051</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>737405</t>
+          <t>739596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>830551</t>
+          <t>832776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>824887</t>
+          <t>830243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>925822</t>
+          <t>927306</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1597520</t>
+          <t>1586082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1731663</t>
+          <t>1728662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1616797</t>
+          <t>1614572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1709943</t>
+          <t>1707752</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1814042</t>
+          <t>1812558</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1914977</t>
+          <t>1909621</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3455549</t>
+          <t>3458550</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3589692</t>
+          <t>3601130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124525</t>
+          <t>123268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162612</t>
+          <t>163485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95716</t>
+          <t>96262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198373</t>
+          <t>197050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251364</t>
+          <t>248179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232732</t>
+          <t>231859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270819</t>
+          <t>272076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196316</t>
+          <t>195770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229187</t>
+          <t>228922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>436012</t>
+          <t>439197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>489003</t>
+          <t>490326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127094</t>
+          <t>126061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77635</t>
+          <t>78795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113547</t>
+          <t>112508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176522</t>
+          <t>175011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227269</t>
+          <t>226065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>255710</t>
+          <t>256743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292764</t>
+          <t>293112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199954</t>
+          <t>200993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235866</t>
+          <t>234706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>469036</t>
+          <t>470240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>519783</t>
+          <t>521294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136426</t>
+          <t>134999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178655</t>
+          <t>179991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>59470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87177</t>
+          <t>87806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202975</t>
+          <t>204684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256518</t>
+          <t>258337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>356833</t>
+          <t>355497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399062</t>
+          <t>400489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153489</t>
+          <t>152860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181245</t>
+          <t>181196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519635</t>
+          <t>517816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573178</t>
+          <t>571469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252460</t>
+          <t>254076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311450</t>
+          <t>309384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202689</t>
+          <t>205020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256805</t>
+          <t>256503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470853</t>
+          <t>472236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>546720</t>
+          <t>549121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>660326</t>
+          <t>662392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>719316</t>
+          <t>717700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441127</t>
+          <t>441429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>495243</t>
+          <t>492912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122987</t>
+          <t>1120586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1198854</t>
+          <t>1197471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94550</t>
+          <t>96604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133395</t>
+          <t>132908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164308</t>
+          <t>163463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207826</t>
+          <t>211783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271547</t>
+          <t>272358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330233</t>
+          <t>330846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269917</t>
+          <t>270404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>308762</t>
+          <t>306708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>461997</t>
+          <t>458040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505515</t>
+          <t>506360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>742902</t>
+          <t>742289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>801588</t>
+          <t>800777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85910</t>
+          <t>86691</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226082</t>
+          <t>222334</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278845</t>
+          <t>276224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>293109</t>
+          <t>291302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>354487</t>
+          <t>350945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134379</t>
+          <t>133598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161558</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>647620</t>
+          <t>650241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>700383</t>
+          <t>704131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>792268</t>
+          <t>795810</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>853646</t>
+          <t>855453</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>818894</t>
+          <t>822372</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>925199</t>
+          <t>924117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>861690</t>
+          <t>863596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>964865</t>
+          <t>967388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1716983</t>
+          <t>1714398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1861944</t>
+          <t>1863697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1983814</t>
+          <t>1984896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2090119</t>
+          <t>2086641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2175554</t>
+          <t>2173031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2278729</t>
+          <t>2276823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4187488</t>
+          <t>4185735</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4332449</t>
+          <t>4335034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75713</t>
+          <t>77707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112288</t>
+          <t>113422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>52303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81071</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137296</t>
+          <t>137674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181558</t>
+          <t>182455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275326</t>
+          <t>274192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311901</t>
+          <t>309907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234745</t>
+          <t>235042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262948</t>
+          <t>263513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521872</t>
+          <t>520975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566134</t>
+          <t>565756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68065</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99721</t>
+          <t>100441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79266</t>
+          <t>79053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113813</t>
+          <t>114973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156368</t>
+          <t>155611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201231</t>
+          <t>201740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216937</t>
+          <t>216217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248593</t>
+          <t>248731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219762</t>
+          <t>218602</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254309</t>
+          <t>254522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449001</t>
+          <t>448492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493864</t>
+          <t>494621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100806</t>
+          <t>102242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138775</t>
+          <t>139349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>46989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134666</t>
+          <t>134004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177460</t>
+          <t>177531</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>266436</t>
+          <t>265862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304405</t>
+          <t>302969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92127</t>
+          <t>92432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112935</t>
+          <t>113216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367173</t>
+          <t>367102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409967</t>
+          <t>410629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232046</t>
+          <t>229201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>286382</t>
+          <t>285998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202974</t>
+          <t>202197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250333</t>
+          <t>252827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>450733</t>
+          <t>448221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>524318</t>
+          <t>523279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593123</t>
+          <t>593507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>647459</t>
+          <t>650304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433698</t>
+          <t>431204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481057</t>
+          <t>481834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1039218</t>
+          <t>1040257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1112803</t>
+          <t>1115315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98221</t>
+          <t>96266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134871</t>
+          <t>132660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138042</t>
+          <t>139270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181052</t>
+          <t>180803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245865</t>
+          <t>247769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302963</t>
+          <t>303961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290298</t>
+          <t>292509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>326948</t>
+          <t>328903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376429</t>
+          <t>376678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>419439</t>
+          <t>418211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>679687</t>
+          <t>678689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736785</t>
+          <t>734881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48762</t>
+          <t>50639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78490</t>
+          <t>78732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>141266</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186444</t>
+          <t>190744</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>199974</t>
+          <t>197042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>254158</t>
+          <t>252752</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>162816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192786</t>
+          <t>190909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>638845</t>
+          <t>634545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>685697</t>
+          <t>684023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>812679</t>
+          <t>814085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>866863</t>
+          <t>869795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>685036</t>
+          <t>685229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>780318</t>
+          <t>784126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>700881</t>
+          <t>699815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>792990</t>
+          <t>795236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1411081</t>
+          <t>1411321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1545716</t>
+          <t>1552632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1875387</t>
+          <t>1871579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1970669</t>
+          <t>1970476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2062623</t>
+          <t>2060377</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2154732</t>
+          <t>2155798</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3965602</t>
+          <t>3958686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4100237</t>
+          <t>4099997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>74778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113615</t>
+          <t>115441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>62568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90516</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145472</t>
+          <t>146433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192856</t>
+          <t>192233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384867</t>
+          <t>383041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424415</t>
+          <t>423704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350409</t>
+          <t>350492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376556</t>
+          <t>378357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746551</t>
+          <t>747174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793935</t>
+          <t>792974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87337</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51799</t>
+          <t>51641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73991</t>
+          <t>74503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113564</t>
+          <t>112600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154395</t>
+          <t>150767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361081</t>
+          <t>358941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394856</t>
+          <t>393555</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325807</t>
+          <t>325965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671628</t>
+          <t>675256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712459</t>
+          <t>713423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>33651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148959</t>
+          <t>152128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174535</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511770</t>
+          <t>508601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630617</t>
+          <t>627078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128883</t>
+          <t>128597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145582</t>
+          <t>145378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651162</t>
+          <t>650637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>770331</t>
+          <t>779134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>189653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248871</t>
+          <t>243919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>87087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214089</t>
+          <t>216223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>260815</t>
+          <t>266191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437503</t>
+          <t>437854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>749280</t>
+          <t>754232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>807897</t>
+          <t>808498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744780</t>
+          <t>742646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>867674</t>
+          <t>871782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1519517</t>
+          <t>1519166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1696205</t>
+          <t>1690829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63353</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99143</t>
+          <t>98077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124512</t>
+          <t>125730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253058</t>
+          <t>253907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202920</t>
+          <t>207789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>336049</t>
+          <t>357559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339709</t>
+          <t>340775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375499</t>
+          <t>375491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>560280</t>
+          <t>559431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>688826</t>
+          <t>687608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>916141</t>
+          <t>894631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1049270</t>
+          <t>1044401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>63818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91023</t>
+          <t>89347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133021</t>
+          <t>128645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120361</t>
+          <t>119852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180041</t>
+          <t>179740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169378</t>
+          <t>168298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211440</t>
+          <t>212665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>610889</t>
+          <t>615265</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>652887</t>
+          <t>654563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>795985</t>
+          <t>796286</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>855665</t>
+          <t>856174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>450805</t>
+          <t>450966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>652680</t>
+          <t>657423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>507437</t>
+          <t>511613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>695305</t>
+          <t>695988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1029299</t>
+          <t>1031265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1305133</t>
+          <t>1318217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2624067</t>
+          <t>2619324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2825942</t>
+          <t>2825781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2804311</t>
+          <t>2803628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2992179</t>
+          <t>2988003</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5471230</t>
+          <t>5458146</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5747064</t>
+          <t>5745098</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93279</t>
+          <t>95164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>131136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73680</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104395</t>
+          <t>102481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177519</t>
+          <t>175547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224712</t>
+          <t>222356</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258174</t>
+          <t>255166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293023</t>
+          <t>291138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194607</t>
+          <t>196940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429878</t>
+          <t>432234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477071</t>
+          <t>479043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82905</t>
+          <t>84193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119286</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106231</t>
+          <t>106739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140009</t>
+          <t>141944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201349</t>
+          <t>200974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248752</t>
+          <t>248709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180919</t>
+          <t>183004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217300</t>
+          <t>216012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193556</t>
+          <t>191621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227334</t>
+          <t>226826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385018</t>
+          <t>385061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432421</t>
+          <t>432796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132615</t>
+          <t>133233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173369</t>
+          <t>171489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34452</t>
+          <t>33756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>56020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175401</t>
+          <t>175099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220530</t>
+          <t>220971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256898</t>
+          <t>258778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297652</t>
+          <t>297034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>84048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105616</t>
+          <t>106312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349805</t>
+          <t>349364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>394934</t>
+          <t>395236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245222</t>
+          <t>245592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>297669</t>
+          <t>298383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189387</t>
+          <t>190530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>239076</t>
+          <t>237956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>447324</t>
+          <t>448192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>520573</t>
+          <t>520217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>572744</t>
+          <t>572030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>625191</t>
+          <t>624821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357173</t>
+          <t>358293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>406862</t>
+          <t>405719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>946089</t>
+          <t>946445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1019338</t>
+          <t>1018470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>70413</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96989</t>
+          <t>100190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>136036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177003</t>
+          <t>175108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212221</t>
+          <t>213094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262348</t>
+          <t>263632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150938</t>
+          <t>147737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179938</t>
+          <t>177514</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>279077</t>
+          <t>280972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319970</t>
+          <t>320044</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>441659</t>
+          <t>440375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491786</t>
+          <t>490913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52821</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77719</t>
+          <t>76364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>229120</t>
+          <t>226438</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282085</t>
+          <t>282678</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>288798</t>
+          <t>291671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>349448</t>
+          <t>351513</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134514</t>
+          <t>135869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159412</t>
+          <t>161005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>663531</t>
+          <t>662938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>716496</t>
+          <t>719178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>808401</t>
+          <t>806336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>869051</t>
+          <t>866178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>739596</t>
+          <t>740815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>832776</t>
+          <t>829991</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>830243</t>
+          <t>831156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>927306</t>
+          <t>926507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1586082</t>
+          <t>1593723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1728662</t>
+          <t>1730525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1614572</t>
+          <t>1617357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1707752</t>
+          <t>1706533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1812558</t>
+          <t>1813357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1909621</t>
+          <t>1908708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3458550</t>
+          <t>3456687</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3601130</t>
+          <t>3593489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123268</t>
+          <t>123626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163485</t>
+          <t>164172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96262</t>
+          <t>95290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197050</t>
+          <t>196080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248179</t>
+          <t>247866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231859</t>
+          <t>231172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272076</t>
+          <t>271718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195770</t>
+          <t>196742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228922</t>
+          <t>229158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439197</t>
+          <t>439510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490326</t>
+          <t>491296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>87891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126061</t>
+          <t>124505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78795</t>
+          <t>79873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112508</t>
+          <t>112818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175011</t>
+          <t>176849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226065</t>
+          <t>227868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>256743</t>
+          <t>258299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>293112</t>
+          <t>294913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200993</t>
+          <t>200683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234706</t>
+          <t>233628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470240</t>
+          <t>468437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>521294</t>
+          <t>519456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134999</t>
+          <t>136326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179991</t>
+          <t>181369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>58660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87806</t>
+          <t>88760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204684</t>
+          <t>204200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258337</t>
+          <t>254914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>355497</t>
+          <t>354119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400489</t>
+          <t>399162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152860</t>
+          <t>151906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181196</t>
+          <t>182006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517816</t>
+          <t>521239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571469</t>
+          <t>571953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>254076</t>
+          <t>251019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309384</t>
+          <t>310764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205020</t>
+          <t>204822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256503</t>
+          <t>254624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472236</t>
+          <t>464721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>549121</t>
+          <t>548398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>662392</t>
+          <t>661012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>717700</t>
+          <t>720757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441429</t>
+          <t>443308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>492912</t>
+          <t>493110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1120586</t>
+          <t>1121309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1197471</t>
+          <t>1204986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96604</t>
+          <t>95992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132908</t>
+          <t>131526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163463</t>
+          <t>162205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>211783</t>
+          <t>209152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272358</t>
+          <t>268449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330846</t>
+          <t>330877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270404</t>
+          <t>271786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>306708</t>
+          <t>307320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>458040</t>
+          <t>460671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>506360</t>
+          <t>507618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>742289</t>
+          <t>742258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>800777</t>
+          <t>804686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59170</t>
+          <t>58947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86691</t>
+          <t>87449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222334</t>
+          <t>225921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>276224</t>
+          <t>278593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>291302</t>
+          <t>292243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>350945</t>
+          <t>352329</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133598</t>
+          <t>132840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>161342</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>650241</t>
+          <t>647872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>704131</t>
+          <t>700544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>795810</t>
+          <t>794426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>855453</t>
+          <t>854512</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>822372</t>
+          <t>822558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>924117</t>
+          <t>923567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>863596</t>
+          <t>862571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>967388</t>
+          <t>962929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1714398</t>
+          <t>1714613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1863697</t>
+          <t>1864592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1984896</t>
+          <t>1985446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2086641</t>
+          <t>2086455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2173031</t>
+          <t>2177490</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2276823</t>
+          <t>2277848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4185735</t>
+          <t>4184840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4335034</t>
+          <t>4334819</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77707</t>
+          <t>75095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113422</t>
+          <t>112236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>51881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80774</t>
+          <t>80696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137674</t>
+          <t>138428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182455</t>
+          <t>185451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274192</t>
+          <t>275378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309907</t>
+          <t>312519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235042</t>
+          <t>235120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263513</t>
+          <t>263935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520975</t>
+          <t>517979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565756</t>
+          <t>565002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67927</t>
+          <t>66110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100441</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79053</t>
+          <t>79245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114973</t>
+          <t>112963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155611</t>
+          <t>155426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201740</t>
+          <t>202834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216217</t>
+          <t>216993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248731</t>
+          <t>250548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218602</t>
+          <t>220612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254522</t>
+          <t>254330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448492</t>
+          <t>447398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494621</t>
+          <t>494806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102242</t>
+          <t>102875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139349</t>
+          <t>141790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26205</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46989</t>
+          <t>47659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134004</t>
+          <t>132930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177531</t>
+          <t>177707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265862</t>
+          <t>263421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302969</t>
+          <t>302336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>91762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113216</t>
+          <t>112529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367102</t>
+          <t>366926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410629</t>
+          <t>411703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229201</t>
+          <t>229384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>285998</t>
+          <t>287903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202197</t>
+          <t>202789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252827</t>
+          <t>252279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448221</t>
+          <t>447322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523279</t>
+          <t>524475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593507</t>
+          <t>591602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650304</t>
+          <t>650121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431204</t>
+          <t>431752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481834</t>
+          <t>481242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1040257</t>
+          <t>1039061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1115315</t>
+          <t>1116214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96266</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132660</t>
+          <t>133675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139270</t>
+          <t>138562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180803</t>
+          <t>182576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>247769</t>
+          <t>248447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303961</t>
+          <t>303988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>292509</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328903</t>
+          <t>327275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376678</t>
+          <t>374905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418211</t>
+          <t>418919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>678689</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>734881</t>
+          <t>734203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50639</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78732</t>
+          <t>77693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141266</t>
+          <t>140964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>190744</t>
+          <t>188452</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197042</t>
+          <t>198943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252752</t>
+          <t>254177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162816</t>
+          <t>163855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190909</t>
+          <t>192316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>634545</t>
+          <t>636837</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>684023</t>
+          <t>684325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>814085</t>
+          <t>812660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>869795</t>
+          <t>867894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>685229</t>
+          <t>683661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>784126</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>699815</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>795236</t>
+          <t>794197</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1411321</t>
+          <t>1407180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1552632</t>
+          <t>1543917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1871579</t>
+          <t>1881193</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1970476</t>
+          <t>1972044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2060377</t>
+          <t>2061416</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2155798</t>
+          <t>2154075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3958686</t>
+          <t>3967401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4099997</t>
+          <t>4104138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>93938</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>75733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115441</t>
+          <t>114502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76359</t>
+          <t>84482</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62568</t>
+          <t>70649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>100015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>168354</t>
+          <t>178420</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146433</t>
+          <t>156626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192233</t>
+          <t>205461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>406487</t>
+          <t>447325</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383041</t>
+          <t>426761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423704</t>
+          <t>465530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>364566</t>
+          <t>396845</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350492</t>
+          <t>381312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>378357</t>
+          <t>410678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>771053</t>
+          <t>844170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>747174</t>
+          <t>817129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>792974</t>
+          <t>865964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69218</t>
+          <t>74112</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>58577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>91597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51641</t>
+          <t>60528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74503</t>
+          <t>85966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131358</t>
+          <t>146989</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112600</t>
+          <t>126056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150767</t>
+          <t>171224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>379200</t>
+          <t>405220</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358941</t>
+          <t>387735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393555</t>
+          <t>420755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>315466</t>
+          <t>345044</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303103</t>
+          <t>331954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325965</t>
+          <t>357392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>694665</t>
+          <t>750264</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675256</t>
+          <t>726029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713423</t>
+          <t>771197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89097</t>
+          <t>106751</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>87788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152128</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>116016</t>
+          <t>138757</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46563</t>
+          <t>115660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175060</t>
+          <t>160092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>571632</t>
+          <t>357114</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508601</t>
+          <t>334890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627078</t>
+          <t>376077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>138049</t>
+          <t>152827</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128597</t>
+          <t>142831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145378</t>
+          <t>161369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>709681</t>
+          <t>509941</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650637</t>
+          <t>488606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>779134</t>
+          <t>533038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>216799</t>
+          <t>223146</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189653</t>
+          <t>196886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>243919</t>
+          <t>254150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>162098</t>
+          <t>180378</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87087</t>
+          <t>160952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216223</t>
+          <t>201177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>378897</t>
+          <t>403523</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266191</t>
+          <t>367811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437854</t>
+          <t>438984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>781352</t>
+          <t>872553</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754232</t>
+          <t>841549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>808498</t>
+          <t>898813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>796771</t>
+          <t>656412</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742646</t>
+          <t>635613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>871782</t>
+          <t>675838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1578123</t>
+          <t>1528966</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1519166</t>
+          <t>1493505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1690829</t>
+          <t>1564678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79816</t>
+          <t>100286</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63361</t>
+          <t>82081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98077</t>
+          <t>123064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>167411</t>
+          <t>151323</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125730</t>
+          <t>134899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253907</t>
+          <t>171402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>247227</t>
+          <t>251609</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207789</t>
+          <t>225020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>357559</t>
+          <t>281039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>359036</t>
+          <t>409562</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340775</t>
+          <t>386784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375491</t>
+          <t>427767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>645927</t>
+          <t>641514</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>559431</t>
+          <t>621435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>687608</t>
+          <t>657938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004963</t>
+          <t>1051076</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>894631</t>
+          <t>1021646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1044401</t>
+          <t>1077665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813338</t>
+          <t>792837</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813338</t>
+          <t>792837</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813338</t>
+          <t>792837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252190</t>
+          <t>1302685</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252190</t>
+          <t>1302685</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252190</t>
+          <t>1302685</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>109348</t>
+          <t>122111</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89347</t>
+          <t>103575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128645</t>
+          <t>148842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,17 +10418,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>146718</t>
+          <t>156841</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119852</t>
+          <t>129315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179740</t>
+          <t>187943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>194746</t>
+          <t>189858</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168298</t>
+          <t>166741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212665</t>
+          <t>204328</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>634562</t>
+          <t>696631</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>615265</t>
+          <t>669900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>654563</t>
+          <t>715167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>829308</t>
+          <t>886490</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>796286</t>
+          <t>855388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>856174</t>
+          <t>914016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976026</t>
+          <t>1043331</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976026</t>
+          <t>1043331</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976026</t>
+          <t>1043331</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>584294</t>
+          <t>632963</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>450966</t>
+          <t>590543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>657423</t>
+          <t>688310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>604276</t>
+          <t>643176</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>511613</t>
+          <t>601988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>695988</t>
+          <t>686313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1188570</t>
+          <t>1276139</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1031265</t>
+          <t>1209888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1318217</t>
+          <t>1342295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2692453</t>
+          <t>2681633</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2619324</t>
+          <t>2626286</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2825781</t>
+          <t>2724053</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2895340</t>
+          <t>2889274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2803628</t>
+          <t>2846137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2988003</t>
+          <t>2930462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5587793</t>
+          <t>5570907</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5458146</t>
+          <t>5504751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5745098</t>
+          <t>5637158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3276747</t>
+          <t>3314596</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3276747</t>
+          <t>3314596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3276747</t>
+          <t>3314596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3499616</t>
+          <t>3532450</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3499616</t>
+          <t>3532450</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3499616</t>
+          <t>3532450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6776363</t>
+          <t>6847046</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6776363</t>
+          <t>6847046</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6776363</t>
+          <t>6847046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
